--- a/datosNivelesPValues.xlsx
+++ b/datosNivelesPValues.xlsx
@@ -528,10 +528,10 @@
         <v>0.2355509598500092</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9742366375732601</v>
+        <v>0.9561042286310508</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5946918112468517</v>
+        <v>0.4202594255975242</v>
       </c>
       <c r="F2" t="n">
         <v>0.001667262682523684</v>
@@ -586,10 +586,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08925584871772634</v>
+        <v>0.08195846897391808</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04790351722650125</v>
+        <v>0.1961893844906968</v>
       </c>
       <c r="F3" t="n">
         <v>0.592998696496662</v>
@@ -638,55 +638,55 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9742366375732601</v>
+        <v>0.9561042286310508</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08925584871772634</v>
+        <v>0.08195846897391808</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001461915311311361</v>
+        <v>3.910219725833916e-52</v>
       </c>
       <c r="F4" t="n">
-        <v>3.119050083840244e-30</v>
+        <v>5.127662643755172e-30</v>
       </c>
       <c r="G4" t="n">
-        <v>2.887145475080646e-27</v>
+        <v>4.439594197850808e-27</v>
       </c>
       <c r="H4" t="n">
-        <v>2.24328470395749e-19</v>
+        <v>2.9483156026147e-19</v>
       </c>
       <c r="I4" t="n">
-        <v>5.889184968298334e-37</v>
+        <v>1.605742081799153e-36</v>
       </c>
       <c r="J4" t="n">
-        <v>4.082288026219197e-35</v>
+        <v>1.175173603051186e-34</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0001256137002156466</v>
+        <v>0.0001175671126673877</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2830479780098e-19</v>
+        <v>1.477226427493724e-19</v>
       </c>
       <c r="M4" t="n">
-        <v>4.220270053599236e-14</v>
+        <v>4.1837639117542e-14</v>
       </c>
       <c r="N4" t="n">
-        <v>8.073698747390406e-18</v>
+        <v>1.14027276882797e-17</v>
       </c>
       <c r="O4" t="n">
-        <v>4.706927835390267e-73</v>
+        <v>3.776656760991533e-72</v>
       </c>
       <c r="P4" t="n">
-        <v>3.764588977356764e-51</v>
+        <v>1.347174028385669e-50</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.045124060993335e-05</v>
+        <v>4.618943608642994e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>2.999664944556934e-05</v>
+        <v>2.73827699294831e-05</v>
       </c>
     </row>
     <row r="5">
@@ -696,55 +696,55 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5946918112468517</v>
+        <v>0.4202594255975242</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04790351722650125</v>
+        <v>0.1961893844906968</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0001461915311311361</v>
+        <v>3.910219725833916e-52</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01680907426342334</v>
+        <v>6.61525616249765e-30</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0155355359175244</v>
+        <v>5.069742149786389e-29</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1056613321838918</v>
+        <v>2.726503074406421e-15</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07788392419719528</v>
+        <v>5.171397421899768e-32</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1126532157463429</v>
+        <v>3.414786142851344e-32</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1685385434864531</v>
+        <v>0.01077575462949636</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009201983200162973</v>
+        <v>1.777136251804156e-21</v>
       </c>
       <c r="M5" t="n">
-        <v>0.004112069237424422</v>
+        <v>1.881853758588551e-17</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1806141866042551</v>
+        <v>2.251199460839748e-15</v>
       </c>
       <c r="O5" t="n">
-        <v>0.006895883277662701</v>
+        <v>1.81612903501292e-51</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01704548268576334</v>
+        <v>3.654518450262026e-42</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.009927839900939501</v>
+        <v>4.616692917571557e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01421556259207802</v>
+        <v>1.952291380248926e-06</v>
       </c>
     </row>
     <row r="6">
@@ -760,10 +760,10 @@
         <v>0.592998696496662</v>
       </c>
       <c r="D6" t="n">
-        <v>3.119050083840244e-30</v>
+        <v>5.127662643755172e-30</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01680907426342334</v>
+        <v>6.61525616249765e-30</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -818,10 +818,10 @@
         <v>0.4805173342684207</v>
       </c>
       <c r="D7" t="n">
-        <v>2.887145475080646e-27</v>
+        <v>4.439594197850808e-27</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0155355359175244</v>
+        <v>5.069742149786389e-29</v>
       </c>
       <c r="F7" t="n">
         <v>3.384197130284848e-144</v>
@@ -876,10 +876,10 @@
         <v>0.9001839252615759</v>
       </c>
       <c r="D8" t="n">
-        <v>2.24328470395749e-19</v>
+        <v>2.9483156026147e-19</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1056613321838918</v>
+        <v>2.726503074406421e-15</v>
       </c>
       <c r="F8" t="n">
         <v>8.414792958090722e-45</v>
@@ -934,10 +934,10 @@
         <v>0.9488507840781497</v>
       </c>
       <c r="D9" t="n">
-        <v>5.889184968298334e-37</v>
+        <v>1.605742081799153e-36</v>
       </c>
       <c r="E9" t="n">
-        <v>0.07788392419719528</v>
+        <v>5.171397421899768e-32</v>
       </c>
       <c r="F9" t="n">
         <v>3.919245536148146e-86</v>
@@ -992,10 +992,10 @@
         <v>0.7684148530929416</v>
       </c>
       <c r="D10" t="n">
-        <v>4.082288026219197e-35</v>
+        <v>1.175173603051186e-34</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1126532157463429</v>
+        <v>3.414786142851344e-32</v>
       </c>
       <c r="F10" t="n">
         <v>3.83456439615441e-83</v>
@@ -1050,10 +1050,10 @@
         <v>0.2351140243212169</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0001256137002156466</v>
+        <v>0.0001175671126673877</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1685385434864531</v>
+        <v>0.01077575462949636</v>
       </c>
       <c r="F11" t="n">
         <v>6.371084005175784e-05</v>
@@ -1108,10 +1108,10 @@
         <v>0.4066506509000405</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2830479780098e-19</v>
+        <v>1.477226427493724e-19</v>
       </c>
       <c r="E12" t="n">
-        <v>0.009201983200162973</v>
+        <v>1.777136251804156e-21</v>
       </c>
       <c r="F12" t="n">
         <v>1.414481211059426e-112</v>
@@ -1166,10 +1166,10 @@
         <v>0.3161742947349379</v>
       </c>
       <c r="D13" t="n">
-        <v>4.220270053599236e-14</v>
+        <v>4.1837639117542e-14</v>
       </c>
       <c r="E13" t="n">
-        <v>0.004112069237424422</v>
+        <v>1.881853758588551e-17</v>
       </c>
       <c r="F13" t="n">
         <v>4.178227096033808e-74</v>
@@ -1224,10 +1224,10 @@
         <v>0.7897961972770638</v>
       </c>
       <c r="D14" t="n">
-        <v>8.073698747390406e-18</v>
+        <v>1.14027276882797e-17</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1806141866042551</v>
+        <v>2.251199460839748e-15</v>
       </c>
       <c r="F14" t="n">
         <v>4.919213528970133e-45</v>
@@ -1282,10 +1282,10 @@
         <v>0.9083718947369702</v>
       </c>
       <c r="D15" t="n">
-        <v>4.706927835390267e-73</v>
+        <v>3.776656760991533e-72</v>
       </c>
       <c r="E15" t="n">
-        <v>0.006895883277662701</v>
+        <v>1.81612903501292e-51</v>
       </c>
       <c r="F15" t="n">
         <v>9.400259522528961e-52</v>
@@ -1340,10 +1340,10 @@
         <v>0.8046444241533987</v>
       </c>
       <c r="D16" t="n">
-        <v>3.764588977356764e-51</v>
+        <v>1.347174028385669e-50</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01704548268576334</v>
+        <v>3.654518450262026e-42</v>
       </c>
       <c r="F16" t="n">
         <v>1.88339630865428e-54</v>
@@ -1398,10 +1398,10 @@
         <v>0.5887790014649369</v>
       </c>
       <c r="D17" t="n">
-        <v>5.045124060993335e-05</v>
+        <v>4.618943608642994e-05</v>
       </c>
       <c r="E17" t="n">
-        <v>0.009927839900939501</v>
+        <v>4.616692917571557e-07</v>
       </c>
       <c r="F17" t="n">
         <v>0.274496027619279</v>
@@ -1456,10 +1456,10 @@
         <v>0.3294272235796228</v>
       </c>
       <c r="D18" t="n">
-        <v>2.999664944556934e-05</v>
+        <v>2.73827699294831e-05</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01421556259207802</v>
+        <v>1.952291380248926e-06</v>
       </c>
       <c r="F18" t="n">
         <v>0.1218508639673581</v>
